--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXIX/LTAIPT_A63F39B.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>49005</t>
   </si>
@@ -109,28 +109,25 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>AFF3C84737B2BA68950E929D31D0AA6A</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>B81A429E307739FA4EC0C5BB69BE3E17</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Unidad de Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>13/01/2023</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de julio del 2022 al 31 de diciembre del 2022 el Comité de Transparencia del Colegio de Bachilleres del Estado de Tlaxcala, no ha emitido resoluciones derivadas de las solicitudes de información en términos del artículo 40, fracción II de la Ley de Transparencia y Acceso a la Información Pública del Estado de Tlaxcala.</t>
+    <t>Área de Transparencia y Archivo</t>
+  </si>
+  <si>
+    <t>10/07/2023</t>
   </si>
 </sst>
 </file>
@@ -526,7 +523,7 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -535,7 +532,7 @@
     <col min="7" max="7" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="255" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
@@ -705,7 +702,7 @@
         <v>37</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
